--- a/2 Output/Phase1_Baseline_Selected100_Observed/tables/phase1_baseline_indicator_table.xlsx
+++ b/2 Output/Phase1_Baseline_Selected100_Observed/tables/phase1_baseline_indicator_table.xlsx
@@ -853,7 +853,7 @@
     <t>Population</t>
   </si>
   <si>
-    <t>91 observed selected-list LCs from the 100-unit original frame; all consented.</t>
+    <t>93 observed selected-list LCs from the 100-unit original frame; all consented.</t>
   </si>
   <si>
     <t>Mean</t>
@@ -1792,10 +1792,10 @@
         <v>43</v>
       </c>
       <c r="E2" s="1">
-        <v>0.70691392185923818</v>
+        <v>0.70687724249337314</v>
       </c>
       <c r="F2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G2" t="s">
         <v>57</v>
@@ -1824,10 +1824,10 @@
         <v>43</v>
       </c>
       <c r="E3" s="1">
-        <v>0.65477272647095253</v>
+        <v>0.65486559055505256</v>
       </c>
       <c r="F3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G3" t="s">
         <v>57</v>
@@ -1856,10 +1856,10 @@
         <v>43</v>
       </c>
       <c r="E4" s="1">
-        <v>0.61510880062213313</v>
+        <v>0.615209507205153</v>
       </c>
       <c r="F4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G4" t="s">
         <v>57</v>
@@ -1888,10 +1888,10 @@
         <v>43</v>
       </c>
       <c r="E5" s="1">
-        <v>0.52304385131695763</v>
+        <v>0.52456441365422746</v>
       </c>
       <c r="F5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G5" t="s">
         <v>57</v>
@@ -1920,10 +1920,10 @@
         <v>43</v>
       </c>
       <c r="E6" s="1">
-        <v>0.76128336263226937</v>
+        <v>0.76238479569394102</v>
       </c>
       <c r="F6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G6" t="s">
         <v>57</v>
@@ -1952,10 +1952,10 @@
         <v>43</v>
       </c>
       <c r="E7" s="1">
-        <v>0.60293040301773571</v>
+        <v>0.60394265286384086</v>
       </c>
       <c r="F7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G7" t="s">
         <v>57</v>
@@ -1984,10 +1984,10 @@
         <v>43</v>
       </c>
       <c r="E8" s="1">
-        <v>0.69803114464649785</v>
+        <v>0.69959678268560799</v>
       </c>
       <c r="F8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G8" t="s">
         <v>57</v>
@@ -2016,10 +2016,10 @@
         <v>43</v>
       </c>
       <c r="E9" s="1">
-        <v>0.6187458378928048</v>
+        <v>0.61955237837247956</v>
       </c>
       <c r="F9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G9" t="s">
         <v>57</v>
@@ -2381,16 +2381,16 @@
         <v>267</v>
       </c>
       <c r="G2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H2" s="1">
-        <v>55.326190575957298</v>
+        <v>56.888095304369926</v>
       </c>
       <c r="I2" s="1">
-        <v>0.60798011621931092</v>
+        <v>0.61169994950935402</v>
       </c>
       <c r="J2" s="1">
-        <v>0.14957754043813448</v>
+        <v>0.14968527156860387</v>
       </c>
       <c r="K2" s="1">
         <v>0.65238094329833984</v>
@@ -2419,16 +2419,16 @@
         <v>267</v>
       </c>
       <c r="G3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H3" s="1">
-        <v>69.276785999536514</v>
+        <v>70.901785999536514</v>
       </c>
       <c r="I3" s="1">
-        <v>0.76128336263226937</v>
+        <v>0.76238479569394102</v>
       </c>
       <c r="J3" s="1">
-        <v>0.15502124377624124</v>
+        <v>0.15548752964205997</v>
       </c>
       <c r="K3" s="1">
         <v>0.78750002384185791</v>
@@ -2457,16 +2457,16 @@
         <v>267</v>
       </c>
       <c r="G4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H4" s="1">
-        <v>64.329166889190674</v>
+        <v>65.739583551883698</v>
       </c>
       <c r="I4" s="1">
-        <v>0.70691392185923818</v>
+        <v>0.70687724249337314</v>
       </c>
       <c r="J4" s="1">
-        <v>0.13296534764165782</v>
+        <v>0.13565344329067455</v>
       </c>
       <c r="K4" s="1">
         <v>0.69375002384185791</v>
@@ -2495,16 +2495,16 @@
         <v>267</v>
       </c>
       <c r="G5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H5" s="1">
-        <v>59.584318108856678</v>
+        <v>60.902499921619892</v>
       </c>
       <c r="I5" s="1">
-        <v>0.65477272647095253</v>
+        <v>0.65486559055505256</v>
       </c>
       <c r="J5" s="1">
-        <v>0.18985609291917113</v>
+        <v>0.18801402745605739</v>
       </c>
       <c r="K5" s="1">
         <v>0.68999999761581421</v>
@@ -2533,16 +2533,16 @@
         <v>267</v>
       </c>
       <c r="G6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H6" s="1">
-        <v>55.974900856614113</v>
+        <v>57.214484170079231</v>
       </c>
       <c r="I6" s="1">
-        <v>0.61510880062213313</v>
+        <v>0.615209507205153</v>
       </c>
       <c r="J6" s="1">
-        <v>0.15389686215621012</v>
+        <v>0.15164907945155967</v>
       </c>
       <c r="K6" s="1">
         <v>0.6111111044883728</v>
@@ -2571,16 +2571,16 @@
         <v>267</v>
       </c>
       <c r="G7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H7" s="1">
-        <v>47.596990469843149</v>
+        <v>48.784490469843149</v>
       </c>
       <c r="I7" s="1">
-        <v>0.52304385131695763</v>
+        <v>0.52456441365422746</v>
       </c>
       <c r="J7" s="1">
-        <v>0.23968173924985345</v>
+        <v>0.23781652105902376</v>
       </c>
       <c r="K7" s="1">
         <v>0.60416668653488159</v>
@@ -2609,19 +2609,19 @@
         <v>267</v>
       </c>
       <c r="G8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H8" s="1">
-        <v>67.806403964757919</v>
+        <v>69.555570632219315</v>
       </c>
       <c r="I8" s="1">
-        <v>0.74512531829404305</v>
+        <v>0.7479093616367668</v>
       </c>
       <c r="J8" s="1">
-        <v>0.1312622303985769</v>
+        <v>0.1331535272148616</v>
       </c>
       <c r="K8" s="1">
-        <v>0.76599997282028198</v>
+        <v>0.76800000667572021</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -2647,16 +2647,16 @@
         <v>267</v>
       </c>
       <c r="G9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H9" s="1">
-        <v>54.866666674613953</v>
+        <v>56.166666716337204</v>
       </c>
       <c r="I9" s="1">
-        <v>0.60293040301773571</v>
+        <v>0.60394265286384086</v>
       </c>
       <c r="J9" s="1">
-        <v>0.14762195914119644</v>
+        <v>0.14930187344910442</v>
       </c>
       <c r="K9" s="1">
         <v>0.625</v>
@@ -2685,16 +2685,16 @@
         <v>267</v>
       </c>
       <c r="G10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H10" s="1">
-        <v>63.520834162831307</v>
+        <v>65.062500789761543</v>
       </c>
       <c r="I10" s="1">
-        <v>0.69803114464649785</v>
+        <v>0.69959678268560799</v>
       </c>
       <c r="J10" s="1">
-        <v>0.22323413490688793</v>
+        <v>0.22353788220026918</v>
       </c>
       <c r="K10" s="1">
         <v>0.61458331346511841</v>
@@ -2723,16 +2723,16 @@
         <v>267</v>
       </c>
       <c r="G11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H11" s="1">
-        <v>56.305871248245239</v>
+        <v>57.618371188640595</v>
       </c>
       <c r="I11" s="1">
-        <v>0.6187458378928048</v>
+        <v>0.61955237837247956</v>
       </c>
       <c r="J11" s="1">
-        <v>0.11306894426126203</v>
+        <v>0.11352554044223796</v>
       </c>
       <c r="K11" s="1">
         <v>0.64583331346511841</v>
@@ -2761,19 +2761,19 @@
         <v>267</v>
       </c>
       <c r="G12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H12" s="1">
-        <v>61.560060113668442</v>
+        <v>63.080615729093552</v>
       </c>
       <c r="I12" s="1">
-        <v>0.67648417707327957</v>
+        <v>0.67828619063541451</v>
       </c>
       <c r="J12" s="1">
-        <v>0.13003804603503888</v>
+        <v>0.13019283122405506</v>
       </c>
       <c r="K12" s="1">
-        <v>0.72157406806945801</v>
+        <v>0.7181018590927124</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -2799,16 +2799,16 @@
         <v>267</v>
       </c>
       <c r="G13" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H13" s="1">
-        <v>60.852305084466934</v>
+        <v>62.229767173528671</v>
       </c>
       <c r="I13" s="1">
-        <v>0.66870664927985646</v>
+        <v>0.66913728143579221</v>
       </c>
       <c r="J13" s="1">
-        <v>0.11925701973810893</v>
+        <v>0.1196162575566249</v>
       </c>
       <c r="K13" s="1">
         <v>0.66197240352630615</v>
@@ -2837,16 +2837,16 @@
         <v>267</v>
       </c>
       <c r="G14" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H14" s="1">
-        <v>55.586268842220306</v>
+        <v>56.892518818378449</v>
       </c>
       <c r="I14" s="1">
-        <v>0.61083811914527808</v>
+        <v>0.61174751417611239</v>
       </c>
       <c r="J14" s="1">
-        <v>0.1140993054736094</v>
+        <v>0.11564632286582086</v>
       </c>
       <c r="K14" s="1">
         <v>0.61979168653488159</v>
@@ -2875,16 +2875,16 @@
         <v>267</v>
       </c>
       <c r="G15" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H15" s="1">
-        <v>58.331206023693085</v>
+        <v>59.772749125957489</v>
       </c>
       <c r="I15" s="1">
-        <v>0.6410022639966273</v>
+        <v>0.64271773253717734</v>
       </c>
       <c r="J15" s="1">
-        <v>0.090111861536896473</v>
+        <v>0.09105181114571495</v>
       </c>
       <c r="K15" s="1">
         <v>0.64100688695907593</v>
@@ -2913,16 +2913,16 @@
         <v>268</v>
       </c>
       <c r="G16" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H16" s="1">
         <v>27</v>
       </c>
       <c r="I16" s="1">
-        <v>0.2967032967032967</v>
+        <v>0.29032258064516131</v>
       </c>
       <c r="J16" s="1">
-        <v>0.45933540141057161</v>
+        <v>0.45637144390360274</v>
       </c>
       <c r="K16" s="1">
         <v>0</v>
@@ -2951,16 +2951,16 @@
         <v>268</v>
       </c>
       <c r="G17" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H17" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" s="1">
-        <v>0.25274725274725274</v>
+        <v>0.25806451612903225</v>
       </c>
       <c r="J17" s="1">
-        <v>0.43699495530794286</v>
+        <v>0.43994134506405991</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
@@ -2989,16 +2989,16 @@
         <v>268</v>
       </c>
       <c r="G18" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H18" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I18" s="1">
-        <v>0.076923076923076927</v>
+        <v>0.086021505376344093</v>
       </c>
       <c r="J18" s="1">
-        <v>0.2679456508228335</v>
+        <v>0.28191557395227324</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -3027,16 +3027,16 @@
         <v>268</v>
       </c>
       <c r="G19" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H19" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I19" s="1">
-        <v>0.087912087912087919</v>
+        <v>0.096774193548387094</v>
       </c>
       <c r="J19" s="1">
-        <v>0.28473580925918163</v>
+        <v>0.29725249584033769</v>
       </c>
       <c r="K19" s="1">
         <v>0</v>
@@ -3065,16 +3065,16 @@
         <v>269</v>
       </c>
       <c r="G20" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H20" s="1">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I20" s="1">
-        <v>0.87912087912087911</v>
+        <v>0.89247311827956988</v>
       </c>
       <c r="J20" s="1">
-        <v>1.4050319477203264</v>
+        <v>1.4023455940068368</v>
       </c>
       <c r="K20" s="1">
         <v>1</v>
@@ -3103,16 +3103,16 @@
         <v>269</v>
       </c>
       <c r="G21" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H21" s="1">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I21" s="1">
-        <v>1.9662921348314606</v>
+        <v>2.0109890109890109</v>
       </c>
       <c r="J21" s="1">
-        <v>2.5648384593923934</v>
+        <v>2.5755021322474638</v>
       </c>
       <c r="K21" s="1">
         <v>1</v>
@@ -3141,16 +3141,16 @@
         <v>269</v>
       </c>
       <c r="G22" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H22" s="1">
         <v>22</v>
       </c>
       <c r="I22" s="1">
-        <v>0.24175824175824176</v>
+        <v>0.23655913978494625</v>
       </c>
       <c r="J22" s="1">
-        <v>0.56451866105676141</v>
+        <v>0.55946110449496866</v>
       </c>
       <c r="K22" s="1">
         <v>0</v>
@@ -3179,16 +3179,16 @@
         <v>269</v>
       </c>
       <c r="G23" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H23" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I23" s="1">
-        <v>0.20634920634920634</v>
+        <v>0.2153846153846154</v>
       </c>
       <c r="J23" s="1">
-        <v>0.54354660181637982</v>
+        <v>0.54464173121843629</v>
       </c>
       <c r="K23" s="1">
         <v>0</v>
@@ -3224,7 +3224,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25">
@@ -3254,7 +3254,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26">
@@ -3277,16 +3277,16 @@
         <v>267</v>
       </c>
       <c r="G26" s="1">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H26" s="1">
         <v>4.7833333333333332</v>
       </c>
       <c r="I26" s="1">
-        <v>0.079722222222222222</v>
+        <v>0.0771505376344086</v>
       </c>
       <c r="J26" s="1">
-        <v>0.20961114717366569</v>
+        <v>0.20663479991774578</v>
       </c>
       <c r="K26" s="1">
         <v>0</v>
@@ -3315,16 +3315,16 @@
         <v>267</v>
       </c>
       <c r="G27" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H27" s="1">
-        <v>33.399999999999999</v>
+        <v>34.600000000000001</v>
       </c>
       <c r="I27" s="1">
-        <v>0.53015873015873016</v>
+        <v>0.53230769230769237</v>
       </c>
       <c r="J27" s="1">
-        <v>0.35769644755282359</v>
+        <v>0.35929953220976202</v>
       </c>
       <c r="K27" s="1">
         <v>0.40000000000000002</v>
@@ -3353,16 +3353,16 @@
         <v>268</v>
       </c>
       <c r="G28" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H28" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I28" s="1">
-        <v>0.87912087912087911</v>
+        <v>0.88172043010752688</v>
       </c>
       <c r="J28" s="1">
-        <v>0.32779278126296108</v>
+        <v>0.324689228192376</v>
       </c>
       <c r="K28" s="1">
         <v>1</v>
@@ -3391,19 +3391,19 @@
         <v>267</v>
       </c>
       <c r="G29" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H29" s="1">
-        <v>65.5</v>
+        <v>65.75</v>
       </c>
       <c r="I29" s="1">
-        <v>0.76162790697674421</v>
+        <v>0.74715909090909094</v>
       </c>
       <c r="J29" s="1">
-        <v>0.28155810377304646</v>
+        <v>0.29481710232693664</v>
       </c>
       <c r="K29" s="1">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
@@ -3429,16 +3429,16 @@
         <v>267</v>
       </c>
       <c r="G30" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H30" s="1">
-        <v>39.75</v>
+        <v>41.5</v>
       </c>
       <c r="I30" s="1">
-        <v>0.45170454545454547</v>
+        <v>0.46111111111111114</v>
       </c>
       <c r="J30" s="1">
-        <v>0.26764714114484656</v>
+        <v>0.27001641416791661</v>
       </c>
       <c r="K30" s="1">
         <v>0.5</v>
@@ -3467,16 +3467,16 @@
         <v>267</v>
       </c>
       <c r="G31" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H31" s="1">
-        <v>37.75</v>
+        <v>38</v>
       </c>
       <c r="I31" s="1">
-        <v>0.42897727272727271</v>
+        <v>0.42222222222222222</v>
       </c>
       <c r="J31" s="1">
-        <v>0.28097956637256255</v>
+        <v>0.2770339604289721</v>
       </c>
       <c r="K31" s="1">
         <v>0.25</v>
@@ -3505,16 +3505,16 @@
         <v>267</v>
       </c>
       <c r="G32" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H32" s="1">
-        <v>66.25</v>
+        <v>68</v>
       </c>
       <c r="I32" s="1">
-        <v>0.7443820224719101</v>
+        <v>0.74725274725274726</v>
       </c>
       <c r="J32" s="1">
-        <v>0.28198144303941425</v>
+        <v>0.28011531726164307</v>
       </c>
       <c r="K32" s="1">
         <v>0.75</v>
@@ -3543,16 +3543,16 @@
         <v>267</v>
       </c>
       <c r="G33" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H33" s="1">
-        <v>60.75</v>
+        <v>62.5</v>
       </c>
       <c r="I33" s="1">
-        <v>0.69827586206896552</v>
+        <v>0.702247191011236</v>
       </c>
       <c r="J33" s="1">
-        <v>0.30293604704067806</v>
+        <v>0.30122006757740777</v>
       </c>
       <c r="K33" s="1">
         <v>0.75</v>
@@ -3581,16 +3581,16 @@
         <v>267</v>
       </c>
       <c r="G34" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H34" s="1">
-        <v>54</v>
+        <v>55.25</v>
       </c>
       <c r="I34" s="1">
-        <v>0.59340659340659341</v>
+        <v>0.59408602150537637</v>
       </c>
       <c r="J34" s="1">
-        <v>0.21294349683644448</v>
+        <v>0.21147122611927807</v>
       </c>
       <c r="K34" s="1">
         <v>0.75</v>
@@ -3619,16 +3619,16 @@
         <v>267</v>
       </c>
       <c r="G35" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H35" s="1">
-        <v>53</v>
+        <v>54.5</v>
       </c>
       <c r="I35" s="1">
-        <v>0.58241758241758246</v>
+        <v>0.58602150537634412</v>
       </c>
       <c r="J35" s="1">
-        <v>0.22685943106955342</v>
+        <v>0.22570729306158335</v>
       </c>
       <c r="K35" s="1">
         <v>0.75</v>
@@ -3657,16 +3657,16 @@
         <v>267</v>
       </c>
       <c r="G36" s="1">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H36" s="1">
-        <v>38</v>
+        <v>39.5</v>
       </c>
       <c r="I36" s="1">
-        <v>0.71698113207547165</v>
+        <v>0.71818181818181814</v>
       </c>
       <c r="J36" s="1">
-        <v>0.41031687991703142</v>
+        <v>0.40555901479083717</v>
       </c>
       <c r="K36" s="1">
         <v>1</v>
@@ -3695,22 +3695,22 @@
         <v>267</v>
       </c>
       <c r="G37" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H37" s="1">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="I37" s="1">
-        <v>0.69090909090909092</v>
+        <v>0.6875</v>
       </c>
       <c r="J37" s="1">
-        <v>0.42481923269948652</v>
+        <v>0.42171187923854964</v>
       </c>
       <c r="K37" s="1">
         <v>1</v>
       </c>
       <c r="L37" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38">
@@ -3733,16 +3733,16 @@
         <v>267</v>
       </c>
       <c r="G38" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H38" s="1">
-        <v>58.25</v>
+        <v>60</v>
       </c>
       <c r="I38" s="1">
-        <v>0.66954022988505746</v>
+        <v>0.6741573033707865</v>
       </c>
       <c r="J38" s="1">
-        <v>0.30617257652923652</v>
+        <v>0.3024626535502285</v>
       </c>
       <c r="K38" s="1">
         <v>0.75</v>
@@ -3771,16 +3771,16 @@
         <v>267</v>
       </c>
       <c r="G39" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H39" s="1">
         <v>54.75</v>
       </c>
       <c r="I39" s="1">
-        <v>0.62215909090909094</v>
+        <v>0.60833333333333328</v>
       </c>
       <c r="J39" s="1">
-        <v>0.30084726664445521</v>
+        <v>0.30226207097577062</v>
       </c>
       <c r="K39" s="1">
         <v>0.5</v>
@@ -3809,16 +3809,16 @@
         <v>267</v>
       </c>
       <c r="G40" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H40" s="1">
-        <v>58</v>
+        <v>59.25</v>
       </c>
       <c r="I40" s="1">
-        <v>0.67441860465116277</v>
+        <v>0.67329545454545459</v>
       </c>
       <c r="J40" s="1">
-        <v>0.29721691287148116</v>
+        <v>0.29932384181343114</v>
       </c>
       <c r="K40" s="1">
         <v>0.75</v>
@@ -3847,16 +3847,16 @@
         <v>267</v>
       </c>
       <c r="G41" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H41" s="1">
-        <v>51.5</v>
+        <v>53</v>
       </c>
       <c r="I41" s="1">
-        <v>0.58522727272727271</v>
+        <v>0.58888888888888891</v>
       </c>
       <c r="J41" s="1">
-        <v>0.31687764516650524</v>
+        <v>0.31647441433919393</v>
       </c>
       <c r="K41" s="1">
         <v>0.5</v>
@@ -3885,16 +3885,16 @@
         <v>267</v>
       </c>
       <c r="G42" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H42" s="1">
-        <v>58.5</v>
+        <v>59.75</v>
       </c>
       <c r="I42" s="1">
-        <v>0.67241379310344829</v>
+        <v>0.6713483146067416</v>
       </c>
       <c r="J42" s="1">
-        <v>0.24205498855003318</v>
+        <v>0.2430730857695608</v>
       </c>
       <c r="K42" s="1">
         <v>0.75</v>
@@ -3923,16 +3923,16 @@
         <v>267</v>
       </c>
       <c r="G43" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H43" s="1">
-        <v>58.25</v>
+        <v>59.75</v>
       </c>
       <c r="I43" s="1">
-        <v>0.66954022988505746</v>
+        <v>0.6713483146067416</v>
       </c>
       <c r="J43" s="1">
-        <v>0.22713538656020449</v>
+        <v>0.22799616728853919</v>
       </c>
       <c r="K43" s="1">
         <v>0.75</v>
@@ -3961,16 +3961,16 @@
         <v>267</v>
       </c>
       <c r="G44" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H44" s="1">
-        <v>45.25</v>
+        <v>46.75</v>
       </c>
       <c r="I44" s="1">
-        <v>0.52011494252873558</v>
+        <v>0.5252808988764045</v>
       </c>
       <c r="J44" s="1">
-        <v>0.28585446879883492</v>
+        <v>0.28960431425575567</v>
       </c>
       <c r="K44" s="1">
         <v>0.5</v>
@@ -3999,22 +3999,22 @@
         <v>267</v>
       </c>
       <c r="G45" s="1">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H45" s="1">
-        <v>53.5</v>
+        <v>55.5</v>
       </c>
       <c r="I45" s="1">
-        <v>0.60795454545454541</v>
+        <v>0.60989010989010994</v>
       </c>
       <c r="J45" s="1">
-        <v>0.30275424991429983</v>
+        <v>0.30324355633162997</v>
       </c>
       <c r="K45" s="1">
         <v>0.5</v>
       </c>
       <c r="L45" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -4037,16 +4037,16 @@
         <v>267</v>
       </c>
       <c r="G46" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H46" s="1">
-        <v>54.75</v>
+        <v>55.75</v>
       </c>
       <c r="I46" s="1">
-        <v>0.60164835164835162</v>
+        <v>0.59946236559139787</v>
       </c>
       <c r="J46" s="1">
-        <v>0.19357033597500153</v>
+        <v>0.19553363766769274</v>
       </c>
       <c r="K46" s="1">
         <v>0.75</v>
@@ -4075,16 +4075,16 @@
         <v>267</v>
       </c>
       <c r="G47" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H47" s="1">
-        <v>54.25</v>
+        <v>55.5</v>
       </c>
       <c r="I47" s="1">
-        <v>0.59615384615384615</v>
+        <v>0.59677419354838712</v>
       </c>
       <c r="J47" s="1">
-        <v>0.21975121908785461</v>
+        <v>0.21817006375323944</v>
       </c>
       <c r="K47" s="1">
         <v>0.75</v>
@@ -4113,16 +4113,16 @@
         <v>267</v>
       </c>
       <c r="G48" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H48" s="1">
-        <v>55.75</v>
+        <v>56.75</v>
       </c>
       <c r="I48" s="1">
-        <v>0.61263736263736268</v>
+        <v>0.61021505376344087</v>
       </c>
       <c r="J48" s="1">
-        <v>0.22749766868077848</v>
+        <v>0.22860150677840199</v>
       </c>
       <c r="K48" s="1">
         <v>0.75</v>
@@ -4151,16 +4151,16 @@
         <v>267</v>
       </c>
       <c r="G49" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H49" s="1">
-        <v>59</v>
+        <v>60.25</v>
       </c>
       <c r="I49" s="1">
-        <v>0.64835164835164838</v>
+        <v>0.64784946236559138</v>
       </c>
       <c r="J49" s="1">
-        <v>0.18994890386781935</v>
+        <v>0.19586957429773869</v>
       </c>
       <c r="K49" s="1">
         <v>0.75</v>
@@ -4189,16 +4189,16 @@
         <v>267</v>
       </c>
       <c r="G50" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H50" s="1">
-        <v>68.75</v>
+        <v>70.25</v>
       </c>
       <c r="I50" s="1">
-        <v>0.75549450549450547</v>
+        <v>0.7553763440860215</v>
       </c>
       <c r="J50" s="1">
-        <v>0.15355971503159963</v>
+        <v>0.1562923621863633</v>
       </c>
       <c r="K50" s="1">
         <v>0.75</v>
@@ -4227,16 +4227,16 @@
         <v>267</v>
       </c>
       <c r="G51" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H51" s="1">
-        <v>48.75</v>
+        <v>50</v>
       </c>
       <c r="I51" s="1">
-        <v>0.5357142857142857</v>
+        <v>0.53763440860215051</v>
       </c>
       <c r="J51" s="1">
-        <v>0.29947043206724045</v>
+        <v>0.30159502738326027</v>
       </c>
       <c r="K51" s="1">
         <v>0.5</v>
@@ -4265,16 +4265,16 @@
         <v>267</v>
       </c>
       <c r="G52" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H52" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I52" s="1">
-        <v>0.40659340659340659</v>
+        <v>0.40860215053763443</v>
       </c>
       <c r="J52" s="1">
-        <v>0.23466391939783812</v>
+        <v>0.2354024832616676</v>
       </c>
       <c r="K52" s="1">
         <v>0.25</v>
@@ -4303,16 +4303,16 @@
         <v>267</v>
       </c>
       <c r="G53" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H53" s="1">
-        <v>63.25</v>
+        <v>65</v>
       </c>
       <c r="I53" s="1">
-        <v>0.70277777777777772</v>
+        <v>0.70652173913043481</v>
       </c>
       <c r="J53" s="1">
-        <v>0.19070553675186055</v>
+        <v>0.1911816050660301</v>
       </c>
       <c r="K53" s="1">
         <v>0.75</v>
@@ -4341,16 +4341,16 @@
         <v>268</v>
       </c>
       <c r="G54" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H54" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I54" s="1">
-        <v>0.92307692307692313</v>
+        <v>0.92473118279569888</v>
       </c>
       <c r="J54" s="1">
-        <v>0.26794565082283345</v>
+        <v>0.26525455943239268</v>
       </c>
       <c r="K54" s="1">
         <v>1</v>
@@ -4379,16 +4379,16 @@
         <v>267</v>
       </c>
       <c r="G55" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H55" s="1">
-        <v>54</v>
+        <v>55.5</v>
       </c>
       <c r="I55" s="1">
-        <v>0.59340659340659341</v>
+        <v>0.59677419354838712</v>
       </c>
       <c r="J55" s="1">
-        <v>0.22866870640596473</v>
+        <v>0.22731973885831891</v>
       </c>
       <c r="K55" s="1">
         <v>0.75</v>
@@ -4417,16 +4417,16 @@
         <v>267</v>
       </c>
       <c r="G56" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H56" s="1">
-        <v>53.5</v>
+        <v>55</v>
       </c>
       <c r="I56" s="1">
-        <v>0.58791208791208793</v>
+        <v>0.59139784946236562</v>
       </c>
       <c r="J56" s="1">
-        <v>0.2278328650739713</v>
+        <v>0.22657943898164717</v>
       </c>
       <c r="K56" s="1">
         <v>0.75</v>
@@ -4455,16 +4455,16 @@
         <v>268</v>
       </c>
       <c r="G57" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H57" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I57" s="1">
-        <v>0.45054945054945056</v>
+        <v>0.45161290322580644</v>
       </c>
       <c r="J57" s="1">
-        <v>0.5003051571843431</v>
+        <v>0.5003505082799905</v>
       </c>
       <c r="K57" s="1">
         <v>0</v>
@@ -4493,16 +4493,16 @@
         <v>268</v>
       </c>
       <c r="G58" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H58" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I58" s="1">
-        <v>0.8571428571428571</v>
+        <v>0.86021505376344087</v>
       </c>
       <c r="J58" s="1">
-        <v>0.35186577527449836</v>
+        <v>0.34864326633713344</v>
       </c>
       <c r="K58" s="1">
         <v>1</v>
@@ -4531,16 +4531,16 @@
         <v>268</v>
       </c>
       <c r="G59" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H59" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I59" s="1">
-        <v>0.30769230769230771</v>
+        <v>0.31182795698924731</v>
       </c>
       <c r="J59" s="1">
-        <v>0.46409548089225705</v>
+        <v>0.46575078761761957</v>
       </c>
       <c r="K59" s="1">
         <v>0</v>
@@ -4569,16 +4569,16 @@
         <v>268</v>
       </c>
       <c r="G60" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H60" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I60" s="1">
-        <v>0.51648351648351654</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="J60" s="1">
-        <v>0.50249681840092531</v>
+        <v>0.50244842317626415</v>
       </c>
       <c r="K60" s="1">
         <v>1</v>
@@ -4607,16 +4607,16 @@
         <v>268</v>
       </c>
       <c r="G61" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H61" s="1">
         <v>7</v>
       </c>
       <c r="I61" s="1">
-        <v>0.076923076923076927</v>
+        <v>0.075268817204301078</v>
       </c>
       <c r="J61" s="1">
-        <v>0.2679456508228335</v>
+        <v>0.26525455943239268</v>
       </c>
       <c r="K61" s="1">
         <v>0</v>
@@ -4645,16 +4645,16 @@
         <v>268</v>
       </c>
       <c r="G62" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H62" s="1">
         <v>19</v>
       </c>
       <c r="I62" s="1">
-        <v>0.2087912087912088</v>
+        <v>0.20430107526881722</v>
       </c>
       <c r="J62" s="1">
-        <v>0.40869666873240723</v>
+        <v>0.40537529002111211</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
@@ -4683,16 +4683,16 @@
         <v>268</v>
       </c>
       <c r="G63" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H63" s="1">
         <v>7</v>
       </c>
       <c r="I63" s="1">
-        <v>0.076923076923076927</v>
+        <v>0.075268817204301078</v>
       </c>
       <c r="J63" s="1">
-        <v>0.2679456508228335</v>
+        <v>0.26525455943239268</v>
       </c>
       <c r="K63" s="1">
         <v>0</v>
@@ -4721,16 +4721,16 @@
         <v>268</v>
       </c>
       <c r="G64" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H64" s="1">
         <v>2</v>
       </c>
       <c r="I64" s="1">
-        <v>0.02197802197802198</v>
+        <v>0.021505376344086023</v>
       </c>
       <c r="J64" s="1">
-        <v>0.14742395237484896</v>
+        <v>0.1458479422322764</v>
       </c>
       <c r="K64" s="1">
         <v>0</v>
@@ -4759,16 +4759,16 @@
         <v>268</v>
       </c>
       <c r="G65" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H65" s="1">
         <v>3</v>
       </c>
       <c r="I65" s="1">
-        <v>0.032967032967032968</v>
+        <v>0.032258064516129031</v>
       </c>
       <c r="J65" s="1">
-        <v>0.17953950048508055</v>
+        <v>0.17764234361221223</v>
       </c>
       <c r="K65" s="1">
         <v>0</v>
@@ -4797,16 +4797,16 @@
         <v>268</v>
       </c>
       <c r="G66" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H66" s="1">
         <v>52</v>
       </c>
       <c r="I66" s="1">
-        <v>0.5714285714285714</v>
+        <v>0.55913978494623651</v>
       </c>
       <c r="J66" s="1">
-        <v>0.49761335152811931</v>
+        <v>0.49918119023312763</v>
       </c>
       <c r="K66" s="1">
         <v>1</v>
@@ -4835,16 +4835,16 @@
         <v>268</v>
       </c>
       <c r="G67" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H67" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I67" s="1">
-        <v>0.36263736263736263</v>
+        <v>0.36559139784946237</v>
       </c>
       <c r="J67" s="1">
-        <v>0.48342489975138192</v>
+        <v>0.48420589935344344</v>
       </c>
       <c r="K67" s="1">
         <v>0</v>
@@ -4873,16 +4873,16 @@
         <v>268</v>
       </c>
       <c r="G68" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H68" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I68" s="1">
-        <v>0.14285714285714285</v>
+        <v>0.15053763440860216</v>
       </c>
       <c r="J68" s="1">
-        <v>0.35186577527449842</v>
+        <v>0.35953582875036627</v>
       </c>
       <c r="K68" s="1">
         <v>0</v>
@@ -4911,16 +4911,16 @@
         <v>268</v>
       </c>
       <c r="G69" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H69" s="1">
         <v>17</v>
       </c>
       <c r="I69" s="1">
-        <v>0.18681318681318682</v>
+        <v>0.18279569892473119</v>
       </c>
       <c r="J69" s="1">
-        <v>0.39192085119568926</v>
+        <v>0.38859380153316303</v>
       </c>
       <c r="K69" s="1">
         <v>0</v>
@@ -4949,16 +4949,16 @@
         <v>268</v>
       </c>
       <c r="G70" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H70" s="1">
         <v>3</v>
       </c>
       <c r="I70" s="1">
-        <v>0.032967032967032968</v>
+        <v>0.032258064516129031</v>
       </c>
       <c r="J70" s="1">
-        <v>0.17953950048508055</v>
+        <v>0.17764234361221223</v>
       </c>
       <c r="K70" s="1">
         <v>0</v>
@@ -4987,16 +4987,16 @@
         <v>268</v>
       </c>
       <c r="G71" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H71" s="1">
         <v>3</v>
       </c>
       <c r="I71" s="1">
-        <v>0.032967032967032968</v>
+        <v>0.032258064516129031</v>
       </c>
       <c r="J71" s="1">
-        <v>0.17953950048508055</v>
+        <v>0.17764234361221223</v>
       </c>
       <c r="K71" s="1">
         <v>0</v>
@@ -5025,16 +5025,16 @@
         <v>268</v>
       </c>
       <c r="G72" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H72" s="1">
         <v>3</v>
       </c>
       <c r="I72" s="1">
-        <v>0.032967032967032968</v>
+        <v>0.032258064516129031</v>
       </c>
       <c r="J72" s="1">
-        <v>0.17953950048508055</v>
+        <v>0.17764234361221223</v>
       </c>
       <c r="K72" s="1">
         <v>0</v>
@@ -5063,16 +5063,16 @@
         <v>268</v>
       </c>
       <c r="G73" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H73" s="1">
         <v>3</v>
       </c>
       <c r="I73" s="1">
-        <v>0.032967032967032968</v>
+        <v>0.032258064516129031</v>
       </c>
       <c r="J73" s="1">
-        <v>0.17953950048508055</v>
+        <v>0.17764234361221223</v>
       </c>
       <c r="K73" s="1">
         <v>0</v>
@@ -5175,7 +5175,7 @@
         <v>296</v>
       </c>
       <c r="B12">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -5239,10 +5239,10 @@
         <v>271</v>
       </c>
       <c r="F2" s="20">
-        <v>0.58522727272727271</v>
+        <v>0.58888888888888891</v>
       </c>
       <c r="G2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H2" t="s">
         <v>313</v>
@@ -5297,10 +5297,10 @@
         <v>271</v>
       </c>
       <c r="F4" s="22">
-        <v>0.6187458378928048</v>
+        <v>0.61955237837247956</v>
       </c>
       <c r="G4">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s">
         <v>322</v>
@@ -5358,7 +5358,7 @@
         <v>22</v>
       </c>
       <c r="G6">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s">
         <v>331</v>
@@ -5384,10 +5384,10 @@
         <v>271</v>
       </c>
       <c r="F7" s="25">
-        <v>0.60293040301773571</v>
+        <v>0.60394265286384086</v>
       </c>
       <c r="G7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s">
         <v>322</v>
@@ -5413,10 +5413,10 @@
         <v>270</v>
       </c>
       <c r="F8" s="26">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="G8">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
         <v>331</v>
@@ -5442,10 +5442,10 @@
         <v>270</v>
       </c>
       <c r="F9" s="27">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H9" t="s">
         <v>331</v>
@@ -5529,10 +5529,10 @@
         <v>271</v>
       </c>
       <c r="F12" s="30">
-        <v>0.87912087912087911</v>
+        <v>0.88172043010752688</v>
       </c>
       <c r="G12">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H12" t="s">
         <v>352</v>
@@ -5558,10 +5558,10 @@
         <v>271</v>
       </c>
       <c r="F13" s="31">
-        <v>0.087912087912087919</v>
+        <v>0.096774193548387094</v>
       </c>
       <c r="G13">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H13" t="s">
         <v>357</v>
